--- a/excel/23127178_HW06_TestCases.xlsx
+++ b/excel/23127178_HW06_TestCases.xlsx
@@ -9432,7 +9432,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18T17:24:44.986Z</t>
+          <t>2026-08-18T17:50:40.254Z</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18T17:24:46.910Z</t>
+          <t>2026-08-18T17:50:43.163Z</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18T17:24:49.916Z</t>
+          <t>2026-08-18T17:50:48.250Z</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>0.8s</t>
+          <t>0.9s</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>**2.2s**</t>
+          <t>**2.4s**</t>
         </is>
       </c>
     </row>

--- a/excel/23127178_HW06_TestCases.xlsx
+++ b/excel/23127178_HW06_TestCases.xlsx
@@ -4713,17 +4713,17 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>400/422</t>
+          <t>200 / 400 / 422</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>từ chối, **hoặc** lấy giá từ catalog</t>
+          <t>**hai hành vi đều hợp lệ**: từ chối (400), hoặc nhận rồi lấy giá từ catalog (200). Hệ quả kiểm ở TC-107</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>spec §4.2</t>
+          <t>spec §4.2 · FR-07</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>INVALID: bản AI sinh đặt assertion `400/422` trong khi cột expected của chính nó ghi *'hoặc lấy giá từ catalog'* — assertion **nghiêm hơn** expected, nên nếu SUT lấy giá từ catalog và trả 200 thì test đỏ oan (test sai, không phải SUT sai). Đã sửa: nhận cả 200, và chuyển phần khẳng định sang **hệ quả trong giỏ** ở TC-107 — chỗ mà cả hai hành vi hợp lệ đều cho cùng một kết luận kiểm được.</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>**FAIL** (1/1 đỏ)</t>
+          <t>**Pass** (2/2)</t>
         </is>
       </c>
     </row>
@@ -4775,17 +4775,17 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>400/422</t>
+          <t>200 / 400 / 422</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>từ chối, hoặc lấy tên từ catalog</t>
+          <t>**hai hành vi đều hợp lệ**: từ chối, hoặc nhận rồi lấy tên từ catalog. Hệ quả kiểm ở TC-107</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>spec §4.2</t>
+          <t>spec §4.2 · FR-07</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>INVALID: cùng lỗi với TC-020 — assertion `400/422` nghiêm hơn expected đã ghi. Đã sửa tương tự.</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>**FAIL** (1/1 đỏ)</t>
+          <t>**Pass** (2/2)</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>**giỏ không được chứa dòng có `quantity ≤ 0`** sau tất cả case trên</t>
+          <t>**bất biến trạng thái giỏ** sau toàn bộ input sai ở trên</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>không dòng nào `quantity ≤ 0`</t>
+          <t>không dòng nào có `quantity ≤ 0`, `name` rỗng/thiếu, hoặc `price` thiếu — **bất kể** SUT chọn cách từ chối hay cách lấy dữ liệu từ catalog</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>FR-07 — trạng thái giỏ phải luôn hợp lệ, kể cả sau khi bị gửi input sai</t>
+          <t>FR-07 — trạng thái giỏ phải luôn hợp lệ, kể cả sau khi bị bơm input sai</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>**FAIL** (1/2 đỏ)</t>
+          <t>**FAIL** (3/4 đỏ)</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18T17:50:40.254Z</t>
+          <t>2026-08-22T15:00:11.332Z</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>0.8s</t>
+          <t>1.1s</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18T17:50:43.163Z</t>
+          <t>2026-08-22T15:00:13.645Z</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>0.7s</t>
+          <t>1.0s</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18T17:50:48.250Z</t>
+          <t>2026-08-22T15:00:16.102Z</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>0.9s</t>
+          <t>1.1s</t>
         </is>
       </c>
     </row>
@@ -9565,12 +9565,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>**329**</t>
+          <t>**333**</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>**240**</t>
+          <t>**244**</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>**2.4s**</t>
+          <t>**3.2s**</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Bug tìm được</t>
+          <t>Bug tìm được (kèm Issue)</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>BUG-01, 02, 05, 06</t>
+          <t>[BUG-01](https://github.com/DuyITLOR/group05_eshop/issues/323), 02, 05, 06</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>BUG-03, BUG-04</t>
+          <t>[BUG-03](https://github.com/DuyITLOR/group05_eshop/issues/325), [BUG-04](https://github.com/DuyITLOR/group05_eshop/issues/326)</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>BUG-07, 08, 10, 11, 12</t>
+          <t>[BUG-07](https://github.com/DuyITLOR/group05_eshop/issues/329), 08, 10, 11, 12</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>BUG-09</t>
+          <t>[BUG-09](https://github.com/DuyITLOR/group05_eshop/issues/331)</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>BUG-13, 14, 15, 16, 17, 18</t>
+          <t>[BUG-13](https://github.com/DuyITLOR/group05_eshop/issues/335), 14, 15, 16, 17, 18</t>
         </is>
       </c>
     </row>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>**BUG-19**</t>
+          <t>**[BUG-19](https://github.com/DuyITLOR/group05_eshop/issues/341)**</t>
         </is>
       </c>
     </row>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>**BUG-13** (API-03). API-02 **đạt**</t>
+          <t>**[BUG-13](https://github.com/DuyITLOR/group05_eshop/issues/335)** (API-03). API-02 **đạt**</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>**BUG-13**</t>
+          <t>**[BUG-13](https://github.com/DuyITLOR/group05_eshop/issues/335)**</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>**BUG-01**, **BUG-02**, BUG-06. `:id` của API-03 **đạt** (đã kiểm, không phải giả định)</t>
+          <t>**[BUG-01](https://github.com/DuyITLOR/group05_eshop/issues/323)**, **[BUG-02](https://github.com/DuyITLOR/group05_eshop/issues/324)**, [BUG-06](https://github.com/DuyITLOR/group05_eshop/issues/328). `:id` của API-03 **đạt** (đã kiểm, không phải giả định)</t>
         </is>
       </c>
     </row>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>**BUG-10** (API-02). API-03 **đạt** (`:id` URL là nguồn duy nhất)</t>
+          <t>**[BUG-10](https://github.com/DuyITLOR/group05_eshop/issues/332)** (API-02). API-03 **đạt** (`:id` URL là nguồn duy nhất)</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>BUG-02, 03, 04, 12, 18</t>
+          <t>[BUG-02](https://github.com/DuyITLOR/group05_eshop/issues/324), 03, 04, 12, 18</t>
         </is>
       </c>
     </row>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>BUG-09, 11, 17 và **BUG-14** (chuỗi 3 lỗi)</t>
+          <t>[BUG-09](https://github.com/DuyITLOR/group05_eshop/issues/331), 11, 17 và **[BUG-14](https://github.com/DuyITLOR/group05_eshop/issues/336)** (chuỗi 3 lỗi)</t>
         </is>
       </c>
     </row>

--- a/excel/23127178_HW06_TestCases.xlsx
+++ b/excel/23127178_HW06_TestCases.xlsx
@@ -9432,7 +9432,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22T15:00:11.332Z</t>
+          <t>2026-08-22T15:17:35.263Z</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>1.1s</t>
+          <t>0.8s</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22T15:00:13.645Z</t>
+          <t>2026-08-22T15:17:37.764Z</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>1.0s</t>
+          <t>0.9s</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22T15:00:16.102Z</t>
+          <t>2026-08-22T15:17:41.396Z</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>1.1s</t>
+          <t>0.8s</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>**3.2s**</t>
+          <t>**2.5s**</t>
         </is>
       </c>
     </row>

--- a/excel/23127178_HW06_TestCases.xlsx
+++ b/excel/23127178_HW06_TestCases.xlsx
@@ -9432,7 +9432,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22T15:17:35.263Z</t>
+          <t>2026-08-22T17:09:50.309Z</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>0.8s</t>
+          <t>0.9s</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22T15:17:37.764Z</t>
+          <t>2026-08-22T17:09:52.873Z</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>0.9s</t>
+          <t>0.8s</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22T15:17:41.396Z</t>
+          <t>2026-08-22T17:09:55.804Z</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>0.8s</t>
+          <t>1.0s</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>**2.5s**</t>
+          <t>**2.6s**</t>
         </is>
       </c>
     </row>

--- a/excel/23127178_HW06_TestCases.xlsx
+++ b/excel/23127178_HW06_TestCases.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SV thêm</t>
+          <t>AI lượt 2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,21 +527,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>API-02 Pool B POST cart</t>
+          <t>API-01 Pool A GET products</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AI sinh</t>
+          <t>SV tự chọn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>generated.md</t>
+          <t>own.md</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -552,12 +552,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Audit</t>
+          <t>AI sinh</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>audit.md</t>
+          <t>generated.md</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -572,56 +572,56 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SV thêm</t>
+          <t>Audit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>extended.md</t>
+          <t>audit.md</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>API-03 Pool C PUT product</t>
+          <t>API-02 Pool B POST cart</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AI sinh</t>
+          <t>AI lượt 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>generated.md</t>
+          <t>extended.md</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>API-03 Pool C PUT product</t>
+          <t>API-02 Pool B POST cart</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Audit</t>
+          <t>SV tự chọn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>audit.md</t>
+          <t>own.md</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -632,28 +632,88 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SV thêm</t>
+          <t>AI sinh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>extended.md</t>
+          <t>generated.md</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>API-03 Pool C PUT product</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>audit.md</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>API-03 Pool C PUT product</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AI lượt 2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>extended.md</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>API-03 Pool C PUT product</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SV tự chọn</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>own.md</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>TỔNG test case</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="n">
-        <v>136</v>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -667,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3026,7 +3086,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -3088,7 +3148,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -3150,7 +3210,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
@@ -3212,7 +3272,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -3274,7 +3334,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -3336,7 +3396,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
@@ -3398,17 +3458,327 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>AI-2</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>**FAIL** (2/4 đỏ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRODLIST-201</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>**không có cơ chế giới hạn số dòng** — thử `?limit=1`</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>`GET /api/products`</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>không có header</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>`limit=1`</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>200 (≤ mốc) hoặc 400</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>hoặc honor `limit` (1 dòng), hoặc 400 vì tham số không hỗ trợ — **không được im lặng trả toàn bộ bảng**</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>FR-05 *product listing* · spec §3.1 chỉ định nghĩa `search`; DB thật của SUT từng có ~900k dòng (HW05)</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>**FAIL** (2/4 đỏ)</t>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>**FAIL** (1/2 đỏ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRODLIST-202</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>**phân trang** — thử `?page=2`</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>`GET /api/products`</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>không có header</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>`page=2`</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>200 (khác trang 1) hoặc 400</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>hoặc trả trang 2, hoặc 400 — không được trả y hệt như không phân trang</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>FR-05 · spec §3.1 **im lặng** về phân trang, nên chỉ khẳng định phần suy được: phải phân biệt được có/không có tham số</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>**FAIL** (1/2 đỏ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRODLIST-203</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>tìm chuỗi **chỉ có trong `description`**, không có trong `name`</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>`GET /api/products`</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>không có header</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>`search=HW06 fixture`</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>**0 dòng** — spec §3.1 nói tìm *theo tên*; nếu trả kết quả thì SUT tìm cả `description`, tức lệch spec</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>spec §3.1 *`?search=keyword` để tìm sản phẩm theo tên*</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>**Pass** (3/3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRODLIST-204</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>`search` dài **8000 ký tự** (biên giới hạn URL)</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>`GET /api/products`</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>không có header</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>`search=AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA`</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>200 / 400 / 414</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>200 (0 dòng), 400, hoặc **414 URI Too Long** — tuyệt đối không 500, và response vẫn là JSON</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>spec §3.1 không giới hạn độ dài; 500 nghĩa là input người dùng làm nổ tầng dưới</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>**Pass** (2/2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRODLIST-205</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>**hệ quả** của TC-204: SUT còn phục vụ bình thường</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>`GET /api/products`</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>không có header</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>200 và số dòng = mốc `total_products` — chuỗi 8000 ký tự không được làm chết hay hỏng dữ liệu</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>spec §3.1 (endpoint phải phục vụ được sau mọi input) · cùng cách kiểm hệ quả đã dùng ở TC-106</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>**Pass** (3/3)</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5928,7 +6298,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Security (ngoài SEC-01…07)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -5963,12 +6333,12 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>FR-07/FR-08 — client không được quyết định giá</t>
+          <t>FR-07/FR-08 — client không được quyết định giá. **Không thuộc SEC-01…07**: danh sách SEC của SUT không có mục nào về toàn vẹn giá/tiền — đó là một lỗ hổng của chính danh sách yêu cầu, ghi lại ở traceability</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -5990,7 +6360,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Security (ngoài SEC-01…07)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -6025,12 +6395,12 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>FR-08 — kiểm **tác động**, không chỉ status code</t>
+          <t>FR-08 — kiểm **tác động**, không chỉ status code. Cùng lý do với TC-101: nằm ngoài SEC-01…07</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -6092,7 +6462,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
@@ -6154,7 +6524,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
@@ -6216,7 +6586,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -6278,7 +6648,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -6340,17 +6710,575 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>AI-2</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>**FAIL** (3/4 đỏ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TC-CART-201</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>bước 1: thêm sản phẩm vào giỏ với giá catalog hiện tại</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>`POST /api/cart`</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>user thường</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>`{"id":"{{product_id}}","name":"HW06-Cart-Fixture","price":111000,"quantity":1}`</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>spec §4.2</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>**FAIL** (3/4 đỏ)</t>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>**Pass** (2/2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TC-CART-202</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>bước 2: **admin đổi giá sản phẩm** đó lên 222000</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>`PUT /api/products/{{product_id}}`</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>`{"name":"HW06-Cart-Fixture","price":222000,"description":"đổi giá","imageUrl":"","category`</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>200 — giá trong catalog giờ là 222000</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>spec §3.3</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>**Pass** (1/1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TC-CART-203</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>bước 3: **giá trong giỏ sau khi catalog đổi giá**</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>`GET /api/cart`</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>user thường</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>dòng của `product_id` **không được** giữ giá cũ 111000 — hoặc cập nhật 222000, hoặc giỏ phải báo giá đã thay đổi</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>FR-08 (tiền đơn hàng tính từ giỏ) — nếu giỏ giữ giá cũ thì khách trả giá cũ cho sản phẩm đã tăng giá</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>**FAIL** (1/2 đỏ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>TC-CART-204</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Security SEC-04</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>**XSS**: `name` chứa `&lt;script&gt;` khi thêm vào giỏ</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>`POST /api/cart`</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>user thường</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>`{"id":"{{product_id}}","name":"&lt;script&gt;alert(1)&lt;/script&gt;","price":222000,"quantity":1}`</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>200 / 400</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>từ chối, hoặc nhận rồi **escape** — hệ quả kiểm ở TC-205</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>SEC-04 *dữ liệu người dùng khi hiển thị phải được escape*</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>**Pass** (1/1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TC-CART-205</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Security SEC-04</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>**hệ quả** TC-204: giỏ không được chứa thẻ script nguyên văn</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>`GET /api/cart`</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>user thường</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>không dòng nào có `name` chứa `&lt;script`</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>SEC-04 — payload phải là dữ liệu, không phải markup sống</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>**FAIL** (1/2 đỏ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>TC-CART-206</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Security SEC-03</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>**giỏ của admin** — admin thêm hàng, giỏ user không được thấy</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>`POST /api/cart`</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>`{"id":"{{product_id}}","name":"HW06-Admin-Cart","price":222000,"quantity":9}`</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>200 — admin có giỏ riêng theo `id` trong token</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>SEC-03 (phân biệt theo role/định danh) · spec §4.1</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>**Pass** (1/1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TC-CART-207</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Security SEC-03</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>**hệ quả** TC-206: giỏ user không chứa dòng admin vừa thêm</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>`GET /api/cart`</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>user thường</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>không dòng nào có `name = HW06-Admin-Cart`</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>SEC-03 · FR-07 (giỏ theo từng người dùng)</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>**Pass** (2/2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>TC-CART-208</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Security SEC-02</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>**token của user đã bị xoá** — bước 1: admin xoá user thứ hai</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>`DELETE /api/admin/users/{{user2_id}}`</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>200 — user2 bị xoá khỏi hệ thống</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>spec §6.1 *Xóa người dùng*</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>**Pass** (1/1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TC-CART-209</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Security SEC-02</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>**hệ quả** TC-208: token cũ của user đã xoá còn dùng được không</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>`GET /api/cart`</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>user thứ hai</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>401 / 403</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>401/403 — JWT của người dùng không còn tồn tại phải bị từ chối</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>SEC-02 *API bảo mật phải yêu cầu JWT **hợp lệ***; một token trỏ tới user đã bị xoá không còn hợp lệ</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>**FAIL** (1/1 đỏ)</t>
         </is>
       </c>
     </row>
@@ -6365,7 +7293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8910,7 +9838,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -8972,7 +9900,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -9034,7 +9962,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
@@ -9096,7 +10024,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
@@ -9158,7 +10086,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -9220,7 +10148,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -9282,7 +10210,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AI-2</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
@@ -9344,17 +10272,451 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>AI-2</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>**FAIL** (1/1 đỏ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRODUPD-201</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Security SEC-04</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>`imageUrl` là **`javascript:` URL**</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>`PUT /api/products/{{product_id}}`</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>`{"name":"HW06-JsUrl","price":200000,"description":"d","imageUrl":"javascript:alert(1)","ca`</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>200 / 400</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>từ chối (400), hoặc nhận nhưng phải chặn ở tầng hiển thị — hệ quả kiểm ở TC-202</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>SEC-04 · spec §3.3 nêu `imageUrl` là URL dạng `http://...`</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>**Pass** (1/1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRODUPD-202</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Security SEC-04</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>**hệ quả** TC-201: `imageUrl` có bị lưu nguyên `javascript:`</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>`GET /api/products/{{product_id}}`</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>không có header</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>`imageUrl` **không** bắt đầu bằng `javascript:` — một URL như vậy đi thẳng vào `src`/`href` của frontend là XSS</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>SEC-04 · spec §3.3</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>**FAIL** (1/2 đỏ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRODUPD-203</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>**category_id trỏ danh mục đã xoá** — bước 1: tạo danh mục tạm</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>`POST /api/categories`</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>`{"name":"HW06-Temp-Category"}`</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>200 + `{id}` — lưu `temp_category_id`</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>spec §3.4</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>**Pass** (1/1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRODUPD-204</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>bước 2: xoá danh mục vừa tạo</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>`DELETE /api/categories/{{temp_category_id}}`</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>200 — danh mục không còn tồn tại</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>spec §3.4</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>**Pass** (1/1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRODUPD-205</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>bước 3: PUT sản phẩm trỏ vào **danh mục đã xoá**</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>`PUT /api/products/{{product_id}}`</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>`{"name":"HW06-Orphan-Category","price":200000,"description":"d","imageUrl":"http://x/i.png`</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>400 / 422</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>từ chối — khoá ngoại phải trỏ tới danh mục đang tồn tại</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>spec §3.4 · FR-14 (quản lý danh mục) — sản phẩm mồ côi danh mục thì trang danh mục hiển thị sai</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
         <is>
           <t>**FAIL** (1/1 đỏ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRODUPD-206</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>**hệ quả** TC-205: sản phẩm có bị gắn danh mục không tồn tại</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>`GET /api/products/{{product_id}}`</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>không có header</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>`category_id` **không** trỏ tới danh mục đã xoá</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>FR-14 · spec §3.4</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>**FAIL** (1/2 đỏ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRODUPD-207</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Security SEC-01</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>**SEC-01**: response của `GET :id` sau khi cập nhật có lộ field nội bộ</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>`GET /api/products/{{product_id}}`</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>không có header</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>chỉ chứa field spec §3.3 định nghĩa; **không** có field nội bộ nào khác (SUT dùng `SELECT *`)</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>SEC-01 (không phơi dữ liệu không cần thiết) · spec §3.2/§3.3</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>**Pass** (2/2)</t>
         </is>
       </c>
     </row>
@@ -9432,7 +10794,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22T17:09:50.309Z</t>
+          <t>2026-08-23T10:27:07.895Z</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -9442,27 +10804,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>**29**</t>
+          <t>**31**</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>0.9s</t>
+          <t>1.2s</t>
         </is>
       </c>
     </row>
@@ -9474,7 +10836,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22T17:09:52.873Z</t>
+          <t>2026-08-23T10:27:11.594Z</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -9484,27 +10846,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>98</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>**30**</t>
+          <t>**33**</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>0.8s</t>
+          <t>0.9s</t>
         </is>
       </c>
     </row>
@@ -9516,7 +10878,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22T17:09:55.804Z</t>
+          <t>2026-08-23T10:27:14.506Z</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -9526,27 +10888,27 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>**30**</t>
+          <t>**33**</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>1.0s</t>
+          <t>1.1s</t>
         </is>
       </c>
     </row>
@@ -9560,27 +10922,27 @@
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>**171**</t>
+          <t>**192**</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>**333**</t>
+          <t>**368**</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>**244**</t>
+          <t>**271**</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>**89**</t>
+          <t>**97**</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>**2.6s**</t>
+          <t>**3.2s**</t>
         </is>
       </c>
     </row>

--- a/excel/23127178_HW06_TestCases.xlsx
+++ b/excel/23127178_HW06_TestCases.xlsx
@@ -3485,7 +3485,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>**không có cơ chế giới hạn số dòng** — thử `?limit=1`</t>
+          <t>`?limit=1` — **ghi nhận hành vi** với tham số spec không định nghĩa</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -3505,17 +3505,17 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>200 (≤ mốc) hoặc 400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>hoặc honor `limit` (1 dòng), hoặc 400 vì tham số không hỗ trợ — **không được im lặng trả toàn bộ bảng**</t>
+          <t>200 + mảng JSON đúng schema. **Không** khẳng định phải honor `limit` hay phải trả 400: spec §3.1 chỉ định nghĩa `search`, và bỏ qua query param lạ là hành vi HTTP bình thường</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>FR-05 *product listing* · spec §3.1 chỉ định nghĩa `search`; DB thật của SUT từng có ~900k dòng (HW05)</t>
+          <t>spec §3.1 (chỉ `search` được định nghĩa) — case này là **characterization test**: ghi lại hành vi thật để lần sau đổi thì biết</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>INVALID: bản đầu đặt expected *'phải honor limit hoặc trả 400'* và báo thành BUG-20. Không có yêu cầu nào trong spec/FR đòi phân trang, nên đó là **kết luận không có căn cứ bắt buộc** — đúng họ lỗi #1–#3 của bài. Đã hạ về ghi nhận hành vi; rủi ro hiệu năng chuyển sang mục **đề xuất cải tiến** ở báo cáo §12, không báo là bug.</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>**phân trang** — thử `?page=2`</t>
+          <t>`?page=2` — ghi nhận hành vi, cùng lý do TC-201</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -3567,17 +3567,17 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>200 (khác trang 1) hoặc 400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>hoặc trả trang 2, hoặc 400 — không được trả y hệt như không phân trang</t>
+          <t>200 + mảng JSON. Spec §3.1 **im lặng** về phân trang → không khẳng định SUT sai</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>FR-05 · spec §3.1 **im lặng** về phân trang, nên chỉ khẳng định phần suy được: phải phân biệt được có/không có tham số</t>
+          <t>spec §3.1 — characterization test</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>INVALID: cùng lỗi với TC-201, đã sửa cùng cách.</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>dòng của `product_id` **không được** giữ giá cũ 111000 — hoặc cập nhật 222000, hoặc giỏ phải báo giá đã thay đổi</t>
+          <t>**ghi nhận**: giỏ giữ giá lúc thêm (111000) dù catalog đã là 222000. Đây có thể là **chính sách price-snapshot** hợp lệ — case này ghi lại hành vi và nêu **câu hỏi nghiệp vụ**, không kết luận SUT sai</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>FR-08 (tiền đơn hàng tính từ giỏ) — nếu giỏ giữ giá cũ thì khách trả giá cũ cho sản phẩm đã tăng giá</t>
+          <t>spec §4.1/§4.2 **không định nghĩa** giỏ tham chiếu hay chụp giá; FR-08 chỉ nói tính tiền từ giỏ → không suy ra được bên nào đúng</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>INVALID: bản đầu khẳng định *'giỏ không được giữ giá cũ'* và báo thành BUG-21 mức High. Nhưng price-snapshot là chính sách phổ biến và hợp lệ; spec không nói bên nào. Đã hạ thành **characterization + câu hỏi nghiệp vụ Q-01** (báo cáo §12). Rủi ro thật vẫn còn nhưng nằm ở **BUG-08** (client tự đặt giá) — chỗ đó có căn cứ FR-08 rõ ràng.</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>không dòng nào có `name` chứa `&lt;script`</t>
+          <t>**ghi nhận**: payload được lưu và trả lại nguyên văn, `Content-Type: application/json`. SEC-04 đòi escape **khi hiển thị**, nên tầng API lưu nguyên văn **chưa tự nó** là vi phạm — rủi ro hiện thực hoá ở UI</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>SEC-04 — payload phải là dữ liệu, không phải markup sống</t>
+          <t>SEC-04 *(dữ liệu người dùng khi **hiển thị** trên UI phải được escape, không dùng `innerHTML`)* — nguyên văn README SUT</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>INVALID: bản đầu assert *'giỏ không được chứa thẻ script'* và báo BUG-22 vi phạm SEC-04. Đọc lại nguyên văn SEC-04: nó nói escape **khi hiển thị**, không nói cấm lưu. Đã hạ thành ghi nhận + **rủi ro R-02** (§12): không có tầng nào validate, nên toàn bộ trách nhiệm dồn lên UI.</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23T10:27:07.895Z</t>
+          <t>2026-08-23T10:51:00.632Z</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10809,22 +10809,22 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>**31**</t>
+          <t>**29**</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>1.2s</t>
+          <t>0.9s</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23T10:27:11.594Z</t>
+          <t>2026-08-23T10:51:03.237Z</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -10851,17 +10851,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>**33**</t>
+          <t>**31**</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23T10:27:14.506Z</t>
+          <t>2026-08-23T10:51:06.445Z</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>1.1s</t>
+          <t>0.9s</t>
         </is>
       </c>
     </row>
@@ -10927,22 +10927,22 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>**368**</t>
+          <t>**372**</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>**271**</t>
+          <t>**279**</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>**97**</t>
+          <t>**93**</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>**3.2s**</t>
+          <t>**2.7s**</t>
         </is>
       </c>
     </row>
@@ -11012,7 +11012,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>43 case (`TC-PRODLIST-001…107`)</t>
+          <t>48 case (`TC-PRODLIST-001…205`)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -11223,17 +11223,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>API-01, API-03</t>
+          <t>API-01, API-02, API-03</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>TC-PRODLIST-028 · TC-PRODUPD-006, 007</t>
+          <t>TC-PRODLIST-028 · TC-PRODUPD-006, 007 · **TC-CART-204/205** · **TC-PRODUPD-201/202**</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Không phát hiện lỗi ở **tầng API** (response là JSON, payload là dữ liệu). Rủi ro thật nằm ở tầng UI — ngoài phạm vi bài API</t>
+          <t>**BUG-22** (payload `&lt;script&gt;` lưu nguyên trong giỏ) · **BUG-24** (`imageUrl: javascript:` lưu nguyên) — hai case do sinh viên chọn</t>
         </is>
       </c>
     </row>
